--- a/data/2024/05-bihor/26564-oradea/budget_file.xlsx
+++ b/data/2024/05-bihor/26564-oradea/budget_file.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="P15" s="5" t="inlineStr">
         <is>
-          <t>07.02 trim3: parent 40.000,00 != sum(children) 76.300,00 (4 children); 07.02 total_2024: parent 133.670,00 != sum(children) 242.770,00 (4 children); 07.02 trim1: parent 63.300,00 != sum(children) 112.900,00 (4 children); 07.02 est2024: parent 139.284,14 != sum(children) 252.966,34 (4 children); 07.02 est2027: parent 139.150,47 != sum(children) 252.723,57 (4 children); 07.02 est2026: parent 139.818,82 != sum(children) 253.937,42 (4 children); 07.02 trim2: parent 15.950,00 != sum(children) 27.800,00 (4 children); 07.02 trim4: parent 14.420,00 != sum(children) 25.770,00 (4 children)</t>
+          <t>07.02 trim3: parent 40.000,00 != sum(children) 76.300,00 (4 children); 07.02 est2027: parent 139.150,47 != sum(children) 252.723,57 (4 children); 07.02 est2024: parent 139.284,14 != sum(children) 252.966,34 (4 children); 07.02 trim4: parent 14.420,00 != sum(children) 25.770,00 (4 children); 07.02 trim2: parent 15.950,00 != sum(children) 27.800,00 (4 children); 07.02 est2026: parent 139.818,82 != sum(children) 253.937,42 (4 children); 07.02 trim1: parent 63.300,00 != sum(children) 112.900,00 (4 children); 07.02 total_2024: parent 133.670,00 != sum(children) 242.770,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>11.02 trim3: parent 27.739,00 != sum(children) 25.763,00 (3 children); 11.02 total_2024: parent 120.918,02 != sum(children) 106.507,02 (3 children); 11.02 trim1: parent 32.872,00 != sum(children) 27.491,00 (3 children); 11.02 est2024: parent 112.271,03 != sum(children) 110.637,03 (3 children); 11.02 est2027: parent 113.756,23 != sum(children) 112.122,23 (3 children); 11.02 est2026: parent 113.047,23 != sum(children) 111.413,23 (3 children); 11.02 trim2: parent 32.815,00 != sum(children) 27.491,00 (3 children); 11.02 trim4: parent 27.492,02 != sum(children) 25.762,02 (3 children)</t>
+          <t>11.02 trim3: parent 27.739,00 != sum(children) 25.763,00 (3 children); 11.02 est2027: parent 113.756,23 != sum(children) 112.122,23 (3 children); 11.02 est2024: parent 112.271,03 != sum(children) 110.637,03 (3 children); 11.02 trim4: parent 27.492,02 != sum(children) 25.762,02 (3 children); 11.02 trim2: parent 32.815,00 != sum(children) 27.491,00 (3 children); 11.02 est2026: parent 113.047,23 != sum(children) 111.413,23 (3 children); 11.02 trim1: parent 32.872,00 != sum(children) 27.491,00 (3 children); 11.02 total_2024: parent 120.918,02 != sum(children) 106.507,02 (3 children)</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="P48" s="5" t="inlineStr">
         <is>
-          <t>36.02 trim3: parent 10.988,00 != sum(children) 3.200,00 (2 children); 36.02 total_2024: parent 100.821,12 != sum(children) 15.000,00 (2 children); 36.02 trim1: parent 40.854,12 != sum(children) 5.400,00 (2 children); 36.02 est2024: parent 105.055,61 != sum(children) 15.630,00 (2 children); 36.02 est2027: parent 104.954,79 != sum(children) 15.615,00 (2 children); 36.02 est2026: parent 105.458,89 != sum(children) 15.690,00 (2 children); 36.02 trim2: parent 40.979,00 != sum(children) 3.400,00 (2 children); 36.02 trim4: parent 8.000,00 != sum(children) 3.000,00 (2 children)</t>
+          <t>36.02 trim3: parent 10.988,00 != sum(children) 3.200,00 (2 children); 36.02 est2027: parent 104.954,79 != sum(children) 15.615,00 (2 children); 36.02 est2024: parent 105.055,61 != sum(children) 15.630,00 (2 children); 36.02 trim4: parent 8.000,00 != sum(children) 3.000,00 (2 children); 36.02 trim2: parent 40.979,00 != sum(children) 3.400,00 (2 children); 36.02 est2026: parent 105.458,89 != sum(children) 15.690,00 (2 children); 36.02 trim1: parent 40.854,12 != sum(children) 5.400,00 (2 children); 36.02 total_2024: parent 100.821,12 != sum(children) 15.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P58" s="5" t="inlineStr">
         <is>
-          <t>42.02 trim3: parent 137.189,06 != sum(children) 68.689,06 (8 children); 42.02 total_2024: parent 494.557,55 != sum(children) 306.943,20 (8 children); 42.02 trim1: parent 97.369,51 != sum(children) 74.582,69 (8 children); 42.02 est2024: parent 349.617,95 != sum(children) 154.123,79 (8 children); 42.02 est2027: parent 349.282,44 != sum(children) 153.975,90 (8 children); 42.02 est2026: parent 350.960,08 != sum(children) 154.715,47 (8 children); 42.02 trim2: parent 137.525,71 != sum(children) 98.198,18 (8 children); 42.02 trim4: parent 122.473,27 != sum(children) 65.473,27 (8 children)</t>
+          <t>42.02 trim3: parent 137.189,06 != sum(children) 68.689,06 (8 children); 42.02 est2027: parent 349.282,44 != sum(children) 153.975,90 (8 children); 42.02 est2024: parent 349.617,95 != sum(children) 154.123,79 (8 children); 42.02 trim4: parent 122.473,27 != sum(children) 65.473,27 (8 children); 42.02 trim2: parent 137.525,71 != sum(children) 98.198,18 (8 children); 42.02 est2026: parent 350.960,08 != sum(children) 154.715,47 (8 children); 42.02 trim1: parent 97.369,51 != sum(children) 74.582,69 (8 children); 42.02 total_2024: parent 494.557,55 != sum(children) 306.943,20 (8 children)</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="P72" s="5" t="inlineStr">
         <is>
-          <t>42.02.90 trim3: parent 0,00 != sum(children) 68.500,00 (2 children); 42.02.90 total_2024: parent 0,00 != sum(children) 187.614,35 (2 children); 42.02.90 trim1: parent 0,00 != sum(children) 22.786,82 (2 children); 42.02.90 est2024: parent 0,00 != sum(children) 195.494,16 (2 children); 42.02.90 est2027: parent 0,00 != sum(children) 195.306,54 (2 children); 42.02.90 est2026: parent 0,00 != sum(children) 196.244,61 (2 children); 42.02.90 trim2: parent 0,00 != sum(children) 39.327,53 (2 children); 42.02.90 trim4: parent 0,00 != sum(children) 57.000,00 (2 children)</t>
+          <t>42.02.90 trim3: parent 0,00 != sum(children) 68.500,00 (2 children); 42.02.90 est2027: parent 0,00 != sum(children) 195.306,54 (2 children); 42.02.90 est2024: parent 0,00 != sum(children) 195.494,16 (2 children); 42.02.90 trim4: parent 0,00 != sum(children) 57.000,00 (2 children); 42.02.90 trim2: parent 0,00 != sum(children) 39.327,53 (2 children); 42.02.90 est2026: parent 0,00 != sum(children) 196.244,61 (2 children); 42.02.90 trim1: parent 0,00 != sum(children) 22.786,82 (2 children); 42.02.90 total_2024: parent 0,00 != sum(children) 187.614,35 (2 children)</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P85" s="5" t="inlineStr">
         <is>
-          <t>50.02 trim3: parent 372.398,80 != sum(children) 105.523,64 (3 children); 50.02 total_2024: parent 1.880.250,91 != sum(children) 602.137,95 (3 children); 50.02 trim1: parent 533.073,18 != sum(children) 136.972,96 (3 children); 50.02 est2024: parent 1.328.687,08 != sum(children) 406.235,28 (3 children); 50.02 est2027: parent 1.399.150,35 != sum(children) 463.986,64 (3 children); 50.02 est2026: parent 1.379.927,91 != sum(children) 461.944,84 (3 children); 50.02 trim2: parent 624.705,65 != sum(children) 253.340,97 (3 children); 50.02 trim4: parent 350.073,28 != sum(children) 106.300,38 (3 children)</t>
+          <t>50.02 trim3: parent 372.398,80 != sum(children) 105.523,64 (3 children); 50.02 est2027: parent 1.399.150,35 != sum(children) 463.986,64 (3 children); 50.02 est2024: parent 1.328.687,08 != sum(children) 406.235,28 (3 children); 50.02 trim4: parent 350.073,28 != sum(children) 106.300,38 (3 children); 50.02 trim2: parent 624.705,65 != sum(children) 253.340,97 (3 children); 50.02 est2026: parent 1.379.927,91 != sum(children) 461.944,84 (3 children); 50.02 trim1: parent 533.073,18 != sum(children) 136.972,96 (3 children); 50.02 total_2024: parent 1.880.250,91 != sum(children) 602.137,95 (3 children)</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="P108" s="5" t="inlineStr">
         <is>
-          <t>51.02 trim3: parent 22.430,70 != sum(children) 317,20 (1 children); 51.02 total_2024: parent 88.107,92 != sum(children) 4.013,62 (1 children); 51.02 trim1: parent 21.953,89 != sum(children) 724,69 (1 children); 51.02 est2024: parent 91.808,45 != sum(children) 4.182,19 (1 children); 51.02 est2027: parent 91.720,35 != sum(children) 4.178,18 (1 children); 51.02 est2026: parent 92.160,89 != sum(children) 4.198,25 (1 children); 51.02 trim2: parent 23.158,57 != sum(children) 1.541,73 (1 children); 51.02 trim4: parent 20.564,76 != sum(children) 1.430,00 (1 children)</t>
+          <t>51.02 trim3: parent 22.430,70 != sum(children) 317,20 (1 children); 51.02 est2027: parent 91.720,35 != sum(children) 4.178,18 (1 children); 51.02 est2024: parent 91.808,45 != sum(children) 4.182,19 (1 children); 51.02 trim4: parent 20.564,76 != sum(children) 1.430,00 (1 children); 51.02 trim2: parent 23.158,57 != sum(children) 1.541,73 (1 children); 51.02 est2026: parent 92.160,89 != sum(children) 4.198,25 (1 children); 51.02 trim1: parent 21.953,89 != sum(children) 724,69 (1 children); 51.02 total_2024: parent 88.107,92 != sum(children) 4.013,62 (1 children)</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="P123" s="5" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 2.050,00 != sum(children) 750,00 (6 children); 20.01 total_2024: parent 10.250,00 != sum(children) 4.575,00 (6 children); 20.01 trim1: parent 3.340,00 != sum(children) 1.465,00 (6 children); 20.01 trim2: parent 2.605,00 != sum(children) 1.305,00 (6 children); 20.01 trim4: parent 2.255,00 != sum(children) 1.055,00 (6 children)</t>
+          <t>20.01 trim3: parent 2.050,00 != sum(children) 750,00 (6 children); 20.01 trim4: parent 2.255,00 != sum(children) 1.055,00 (6 children); 20.01 trim2: parent 2.605,00 != sum(children) 1.305,00 (6 children); 20.01 trim1: parent 3.340,00 != sum(children) 1.465,00 (6 children); 20.01 total_2024: parent 10.250,00 != sum(children) 4.575,00 (6 children)</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="P159" s="5" t="inlineStr">
         <is>
-          <t>54.02 trim3: parent 1.040,00 != sum(children) 16,00 (1 children); 54.02 total_2024: parent 19.336,99 != sum(children) 266,00 (1 children); 54.02 est2024: parent 4.435,79 != sum(children) 277,17 (1 children); 54.02 est2027: parent 4.431,53 != sum(children) 276,91 (1 children); 54.02 est2026: parent 4.452,81 != sum(children) 278,24 (1 children); 54.02 trim2: parent 1.277,80 != sum(children) 250,00 (1 children)</t>
+          <t>54.02 trim3: parent 1.040,00 != sum(children) 16,00 (1 children); 54.02 est2027: parent 4.431,53 != sum(children) 276,91 (1 children); 54.02 est2024: parent 4.435,79 != sum(children) 277,17 (1 children); 54.02 trim2: parent 1.277,80 != sum(children) 250,00 (1 children); 54.02 est2026: parent 4.452,81 != sum(children) 278,24 (1 children); 54.02 total_2024: parent 19.336,99 != sum(children) 266,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P198" s="5" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 9.836,90 != sum(children) 319,00 (1 children); 61.02 trim1: parent 2.869,50 != sum(children) 124,00 (1 children); 61.02 est2024: parent 10.250,05 != sum(children) 332,40 (1 children); 61.02 est2027: parent 10.240,22 != sum(children) 332,08 (1 children); 61.02 est2026: parent 10.289,40 != sum(children) 333,68 (1 children); 61.02 trim2: parent 2.807,60 != sum(children) 195,00 (1 children)</t>
+          <t>61.02 est2027: parent 10.240,22 != sum(children) 332,08 (1 children); 61.02 est2024: parent 10.250,05 != sum(children) 332,40 (1 children); 61.02 trim2: parent 2.807,60 != sum(children) 195,00 (1 children); 61.02 est2026: parent 10.289,40 != sum(children) 333,68 (1 children); 61.02 trim1: parent 2.869,50 != sum(children) 124,00 (1 children); 61.02 total_2024: parent 9.836,90 != sum(children) 319,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P212" s="5" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 792,90 != sum(children) 777,90 (7 children); 20 trim1: parent 324,00 != sum(children) 309,00 (7 children)</t>
+          <t>20 trim1: parent 324,00 != sum(children) 309,00 (7 children); 20 total_2024: parent 792,90 != sum(children) 777,90 (7 children)</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P239" s="5" t="inlineStr">
         <is>
-          <t>65.02 trim3: parent 72.882,62 != sum(children) 2.450,00 (2 children); 65.02 total_2024: parent 264.930,18 != sum(children) 25.276,37 (2 children); 65.02 trim1: parent 59.623,74 != sum(children) 11.333,34 (2 children); 65.02 est2024: parent 189.659,12 != sum(children) 24.834,73 (2 children); 65.02 est2027: parent 227.530,09 != sum(children) 24.826,74 (2 children); 65.02 est2026: parent 201.087,48 != sum(children) 24.866,73 (2 children); 65.02 trim2: parent 73.807,61 != sum(children) 10.590,03 (2 children); 65.02 trim4: parent 58.616,21 != sum(children) 903,00 (2 children)</t>
+          <t>65.02 trim3: parent 72.882,62 != sum(children) 2.450,00 (2 children); 65.02 est2027: parent 227.530,09 != sum(children) 24.826,74 (2 children); 65.02 est2024: parent 189.659,12 != sum(children) 24.834,73 (2 children); 65.02 trim4: parent 58.616,21 != sum(children) 903,00 (2 children); 65.02 trim2: parent 73.807,61 != sum(children) 10.590,03 (2 children); 65.02 est2026: parent 201.087,48 != sum(children) 24.866,73 (2 children); 65.02 trim1: parent 59.623,74 != sum(children) 11.333,34 (2 children); 65.02 total_2024: parent 264.930,18 != sum(children) 25.276,37 (2 children)</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="P248" s="5" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 5.011,37 != sum(children) 4.058,02 (7 children); 20.01 total_2024: parent 24.546,80 != sum(children) 19.942,90 (7 children); 20.01 trim1: parent 8.129,03 != sum(children) 6.372,08 (7 children); 20.01 trim2: parent 6.022,48 != sum(children) 5.044,73 (7 children); 20.01 trim4: parent 5.383,92 != sum(children) 4.468,07 (7 children)</t>
+          <t>20.01 trim3: parent 5.011,37 != sum(children) 4.058,02 (7 children); 20.01 trim4: parent 5.383,92 != sum(children) 4.468,07 (7 children); 20.01 trim2: parent 6.022,48 != sum(children) 5.044,73 (7 children); 20.01 trim1: parent 8.129,03 != sum(children) 6.372,08 (7 children); 20.01 total_2024: parent 24.546,80 != sum(children) 19.942,90 (7 children)</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="P286" s="5" t="inlineStr">
         <is>
-          <t>59 total_2024: parent 319,90 != sum(children) 309,90 (3 children); 59 trim2: parent 78,80 != sum(children) 68,80 (3 children)</t>
+          <t>59 trim2: parent 78,80 != sum(children) 68,80 (3 children); 59 total_2024: parent 319,90 != sum(children) 309,90 (3 children)</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="P312" s="5" t="inlineStr">
         <is>
-          <t>66.02 trim3: parent 52.650,00 != sum(children) 800,00 (2 children); 66.02 total_2024: parent 171.081,32 != sum(children) 26.902,17 (2 children); 66.02 trim1: parent 26.927,54 != sum(children) 2.839,92 (2 children); 66.02 est2024: parent 128.336,50 != sum(children) 10.504,91 (2 children); 66.02 est2027: parent 128.221,96 != sum(children) 10.503,46 (2 children); 66.02 est2026: parent 128.794,60 != sum(children) 10.510,68 (2 children); 66.02 trim2: parent 27.913,49 != sum(children) 5.647,81 (2 children); 66.02 trim4: parent 63.590,29 != sum(children) 17.614,44 (2 children)</t>
+          <t>66.02 trim3: parent 52.650,00 != sum(children) 800,00 (2 children); 66.02 est2027: parent 128.221,96 != sum(children) 10.503,46 (2 children); 66.02 est2024: parent 128.336,50 != sum(children) 10.504,91 (2 children); 66.02 trim4: parent 63.590,29 != sum(children) 17.614,44 (2 children); 66.02 trim2: parent 27.913,49 != sum(children) 5.647,81 (2 children); 66.02 est2026: parent 128.794,60 != sum(children) 10.510,68 (2 children); 66.02 trim1: parent 26.927,54 != sum(children) 2.839,92 (2 children); 66.02 total_2024: parent 171.081,32 != sum(children) 26.902,17 (2 children)</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="P315" s="5" t="inlineStr">
         <is>
-          <t>10.01 trim3: parent 2.259,00 != sum(children) 2.175,00 (4 children); 10.01 total_2024: parent 8.726,85 != sum(children) 8.390,85 (4 children); 10.01 trim1: parent 2.215,00 != sum(children) 2.130,00 (4 children); 10.01 trim2: parent 2.362,00 != sum(children) 2.278,00 (4 children); 10.01 trim4: parent 1.890,85 != sum(children) 1.807,85 (4 children)</t>
+          <t>10.01 trim3: parent 2.259,00 != sum(children) 2.175,00 (4 children); 10.01 trim4: parent 1.890,85 != sum(children) 1.807,85 (4 children); 10.01 trim2: parent 2.362,00 != sum(children) 2.278,00 (4 children); 10.01 trim1: parent 2.215,00 != sum(children) 2.130,00 (4 children); 10.01 total_2024: parent 8.726,85 != sum(children) 8.390,85 (4 children)</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="P346" s="5" t="inlineStr">
         <is>
-          <t>60 trim2: parent 12.827,53 != sum(children) 2.212,70 (1 children); 60 trim3: parent 41.000,00 != sum(children) 6.000,00 (1 children); 60 trim4: parent 42.000,00 != sum(children) 7.000,00 (1 children); 60 total_2024: parent 95.827,53 != sum(children) 15.212,70 (1 children)</t>
+          <t>60 trim3: parent 41.000,00 != sum(children) 6.000,00 (1 children); 60 total_2024: parent 95.827,53 != sum(children) 15.212,70 (1 children); 60 trim2: parent 12.827,53 != sum(children) 2.212,70 (1 children); 60 trim4: parent 42.000,00 != sum(children) 7.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="P365" s="5" t="inlineStr">
         <is>
-          <t>67.02 trim3: parent 24.211,12 != sum(children) 7.606,58 (1 children); 67.02 total_2024: parent 98.281,69 != sum(children) 27.660,18 (1 children); 67.02 trim1: parent 23.973,71 != sum(children) 6.772,48 (1 children); 67.02 est2024: parent 101.498,43 != sum(children) 28.821,91 (1 children); 67.02 est2027: parent 101.417,63 != sum(children) 28.794,26 (1 children); 67.02 est2026: parent 101.821,64 != sum(children) 28.932,55 (1 children); 67.02 trim2: parent 29.149,86 != sum(children) 8.654,92 (1 children); 67.02 trim4: parent 20.947,00 != sum(children) 4.626,20 (1 children)</t>
+          <t>67.02 trim3: parent 24.211,12 != sum(children) 7.606,58 (1 children); 67.02 est2027: parent 101.417,63 != sum(children) 28.794,26 (1 children); 67.02 est2024: parent 101.498,43 != sum(children) 28.821,91 (1 children); 67.02 trim4: parent 20.947,00 != sum(children) 4.626,20 (1 children); 67.02 trim2: parent 29.149,86 != sum(children) 8.654,92 (1 children); 67.02 est2026: parent 101.821,64 != sum(children) 28.932,55 (1 children); 67.02 trim1: parent 23.973,71 != sum(children) 6.772,48 (1 children); 67.02 total_2024: parent 98.281,69 != sum(children) 27.660,18 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="P398" s="5" t="inlineStr">
         <is>
-          <t>71 total_2024: parent 27.660,18 != sum(children) 27.110,18 (2 children); 71 trim1: parent 6.772,48 != sum(children) 6.622,48 (2 children); 71 trim2: parent 8.654,92 != sum(children) 8.504,92 (2 children); 71 trim4: parent 4.626,20 != sum(children) 4.376,20 (2 children)</t>
+          <t>71 trim4: parent 4.626,20 != sum(children) 4.376,20 (2 children); 71 trim2: parent 8.654,92 != sum(children) 8.504,92 (2 children); 71 trim1: parent 6.772,48 != sum(children) 6.622,48 (2 children); 71 total_2024: parent 27.660,18 != sum(children) 27.110,18 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P411" s="5" t="inlineStr">
         <is>
-          <t>68.02 trim3: parent 16.130,90 != sum(children) 12.889,00 (3 children); 68.02 total_2024: parent 70.976,99 != sum(children) 57.319,51 (3 children); 68.02 trim1: parent 21.857,30 != sum(children) 17.182,00 (3 children); 68.02 est2024: parent 71.628,73 != sum(children) 57.397,64 (3 children); 68.02 est2027: parent 71.612,72 != sum(children) 57.395,26 (3 children); 68.02 est2026: parent 71.692,91 != sum(children) 57.407,18 (3 children); 68.02 trim2: parent 18.660,00 != sum(children) 15.150,00 (3 children); 68.02 trim4: parent 14.328,79 != sum(children) 12.098,51 (3 children); 68.02 total_2024: parent 70.976,99 != sum(children) 835,00 (1 children); 68.02 trim1: parent 21.857,30 != sum(children) 775,00 (1 children); 68.02 est2024: parent 71.628,73 != sum(children) 870,07 (1 children); 68.02 est2027: parent 71.612,72 != sum(children) 869,24 (1 children); 68.02 est2026: parent 71.692,91 != sum(children) 873,41 (1 children); 68.02 trim2: parent 18.660,00 != sum(children) 60,00 (1 children)</t>
+          <t>68.02 trim3: parent 16.130,90 != sum(children) 12.889,00 (3 children); 68.02 est2027: parent 71.612,72 != sum(children) 57.395,26 (3 children); 68.02 est2024: parent 71.628,73 != sum(children) 57.397,64 (3 children); 68.02 trim4: parent 14.328,79 != sum(children) 12.098,51 (3 children); 68.02 trim2: parent 18.660,00 != sum(children) 15.150,00 (3 children); 68.02 est2026: parent 71.692,91 != sum(children) 57.407,18 (3 children); 68.02 trim1: parent 21.857,30 != sum(children) 17.182,00 (3 children); 68.02 total_2024: parent 70.976,99 != sum(children) 57.319,51 (3 children); 68.02 est2027: parent 71.612,72 != sum(children) 869,24 (1 children); 68.02 est2024: parent 71.628,73 != sum(children) 870,07 (1 children); 68.02 trim2: parent 18.660,00 != sum(children) 60,00 (1 children); 68.02 est2026: parent 71.692,91 != sum(children) 873,41 (1 children); 68.02 trim1: parent 21.857,30 != sum(children) 775,00 (1 children); 68.02 total_2024: parent 70.976,99 != sum(children) 835,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P426" s="5" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 3.540,18 != sum(children) 3.532,18 (9 children); 20 trim1: parent 1.401,00 != sum(children) 1.393,00 (9 children)</t>
+          <t>20 trim1: parent 1.401,00 != sum(children) 1.393,00 (9 children); 20 total_2024: parent 3.540,18 != sum(children) 3.532,18 (9 children)</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23061,7 @@
       </c>
       <c r="P475" s="5" t="inlineStr">
         <is>
-          <t>70.02 trim3: parent 61.899,31 != sum(children) 38.037,11 (3 children); 70.02 total_2024: parent 343.391,66 != sum(children) 193.691,53 (3 children); 70.02 trim1: parent 127.976,36 != sum(children) 64.193,65 (3 children); 70.02 est2024: parent 264.090,49 != sum(children) 169.702,84 (3 children); 70.02 est2027: parent 296.502,92 != sum(children) 202.186,67 (3 children); 70.02 est2026: parent 298.615,69 != sum(children) 203.942,48 (3 children); 70.02 trim2: parent 101.467,10 != sum(children) 60.632,08 (3 children); 70.02 trim4: parent 52.048,89 != sum(children) 30.828,69 (3 children)</t>
+          <t>70.02 trim3: parent 61.899,31 != sum(children) 38.037,11 (3 children); 70.02 est2027: parent 296.502,92 != sum(children) 202.186,67 (3 children); 70.02 est2024: parent 264.090,49 != sum(children) 169.702,84 (3 children); 70.02 trim4: parent 52.048,89 != sum(children) 30.828,69 (3 children); 70.02 trim2: parent 101.467,10 != sum(children) 60.632,08 (3 children); 70.02 est2026: parent 298.615,69 != sum(children) 203.942,48 (3 children); 70.02 trim1: parent 127.976,36 != sum(children) 64.193,65 (3 children); 70.02 total_2024: parent 343.391,66 != sum(children) 193.691,53 (3 children)</t>
         </is>
       </c>
     </row>
@@ -25580,7 +25580,7 @@
       </c>
       <c r="P528" s="5" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 74.355,79 != sum(children) 73.085,79 (2 children); 74.02 trim1: parent 20.429,79 != sum(children) 19.184,79 (2 children); 74.02 est2024: parent 59.292,34 != sum(children) 57.969,00 (2 children); 74.02 est2027: parent 64.283,43 != sum(children) 62.961,35 (2 children); 74.02 est2026: parent 64.328,00 != sum(children) 62.999,58 (2 children); 74.02 trim2: parent 20.542,25 != sum(children) 20.517,25 (2 children); 74.02 trim3: parent 20.956,25 != sum(children) 198,25 (1 children); 74.02 total_2024: parent 74.355,79 != sum(children) 866,20 (1 children); 74.02 trim1: parent 20.429,79 != sum(children) 302,20 (1 children); 74.02 est2024: parent 59.292,34 != sum(children) 902,58 (1 children); 74.02 est2027: parent 64.283,43 != sum(children) 901,71 (1 children); 74.02 est2026: parent 64.328,00 != sum(children) 906,04 (1 children); 74.02 trim2: parent 20.542,25 != sum(children) 334,25 (1 children); 74.02 trim4: parent 12.427,50 != sum(children) 31,50 (1 children)</t>
+          <t>74.02 est2027: parent 64.283,43 != sum(children) 62.961,35 (2 children); 74.02 est2024: parent 59.292,34 != sum(children) 57.969,00 (2 children); 74.02 trim2: parent 20.542,25 != sum(children) 20.517,25 (2 children); 74.02 est2026: parent 64.328,00 != sum(children) 62.999,58 (2 children); 74.02 trim1: parent 20.429,79 != sum(children) 19.184,79 (2 children); 74.02 total_2024: parent 74.355,79 != sum(children) 73.085,79 (2 children); 74.02 trim3: parent 20.956,25 != sum(children) 198,25 (1 children); 74.02 est2027: parent 64.283,43 != sum(children) 901,71 (1 children); 74.02 est2024: parent 59.292,34 != sum(children) 902,58 (1 children); 74.02 trim4: parent 12.427,50 != sum(children) 31,50 (1 children); 74.02 trim2: parent 20.542,25 != sum(children) 334,25 (1 children); 74.02 est2026: parent 64.328,00 != sum(children) 906,04 (1 children); 74.02 trim1: parent 20.429,79 != sum(children) 302,20 (1 children); 74.02 total_2024: parent 74.355,79 != sum(children) 866,20 (1 children)</t>
         </is>
       </c>
     </row>
@@ -26977,7 +26977,7 @@
       </c>
       <c r="P557" s="5" t="inlineStr">
         <is>
-          <t>80.02 trim3: parent 1.487,50 != sum(children) 97.224,00 (2 children); 80.02 total_2024: parent 13.374,46 != sum(children) 704.315,93 (2 children); 80.02 trim1: parent 3.751,80 != sum(children) 213.117,05 (2 children); 80.02 est2024: parent 9.358,41 != sum(children) 367.850,09 (2 children); 80.02 est2027: parent 9.351,30 != sum(children) 375.655,80 (2 children); 80.02 est2026: parent 9.386,86 != sum(children) 372.946,35 (2 children); 80.02 trim2: parent 1.508,43 != sum(children) 306.198,80 (2 children); 80.02 trim4: parent 6.626,73 != sum(children) 87.776,08 (2 children); 80.02 trim3: parent 1.487,50 != sum(children) 487,50 (2 children); 80.02 total_2024: parent 13.374,46 != sum(children) 7.057,13 (2 children); 80.02 trim1: parent 3.751,80 != sum(children) 834,47 (2 children); 80.02 est2024: parent 9.358,41 != sum(children) 2.819,52 (2 children); 80.02 est2027: parent 9.351,30 != sum(children) 2.818,68 (2 children); 80.02 est2026: parent 9.386,86 != sum(children) 2.822,86 (2 children); 80.02 trim2: parent 1.508,43 != sum(children) 108,43 (2 children); 80.02 trim4: parent 6.626,73 != sum(children) 5.626,73 (2 children)</t>
+          <t>80.02 trim3: parent 1.487,50 != sum(children) 97.224,00 (2 children); 80.02 est2027: parent 9.351,30 != sum(children) 375.655,80 (2 children); 80.02 est2024: parent 9.358,41 != sum(children) 367.850,09 (2 children); 80.02 trim4: parent 6.626,73 != sum(children) 87.776,08 (2 children); 80.02 trim2: parent 1.508,43 != sum(children) 306.198,80 (2 children); 80.02 est2026: parent 9.386,86 != sum(children) 372.946,35 (2 children); 80.02 trim1: parent 3.751,80 != sum(children) 213.117,05 (2 children); 80.02 total_2024: parent 13.374,46 != sum(children) 704.315,93 (2 children); 80.02 trim3: parent 1.487,50 != sum(children) 487,50 (2 children); 80.02 est2027: parent 9.351,30 != sum(children) 2.818,68 (2 children); 80.02 est2024: parent 9.358,41 != sum(children) 2.819,52 (2 children); 80.02 trim4: parent 6.626,73 != sum(children) 5.626,73 (2 children); 80.02 trim2: parent 1.508,43 != sum(children) 108,43 (2 children); 80.02 est2026: parent 9.386,86 != sum(children) 2.822,86 (2 children); 80.02 trim1: parent 3.751,80 != sum(children) 834,47 (2 children); 80.02 total_2024: parent 13.374,46 != sum(children) 7.057,13 (2 children)</t>
         </is>
       </c>
     </row>
@@ -27921,7 +27921,7 @@
       </c>
       <c r="P577" s="5" t="inlineStr">
         <is>
-          <t>81.02 trim3: parent 30.788,00 != sum(children) 25.000,00 (2 children); 81.02 total_2024: parent 318.456,97 != sum(children) 135.303,51 (2 children); 81.02 trim1: parent 91.391,45 != sum(children) 10.025,79 (2 children); 81.02 est2024: parent 80.267,73 != sum(children) 24.757,00 (2 children); 81.02 est2027: parent 60.607,79 != sum(children) 24.500,00 (2 children); 81.02 est2026: parent 61.901,52 != sum(children) 25.000,00 (2 children); 81.02 trim2: parent 164.733,52 != sum(children) 74.519,72 (2 children); 81.02 trim4: parent 31.544,00 != sum(children) 25.758,00 (2 children)</t>
+          <t>81.02 trim3: parent 30.788,00 != sum(children) 25.000,00 (2 children); 81.02 est2027: parent 60.607,79 != sum(children) 24.500,00 (2 children); 81.02 est2024: parent 80.267,73 != sum(children) 24.757,00 (2 children); 81.02 trim4: parent 31.544,00 != sum(children) 25.758,00 (2 children); 81.02 trim2: parent 164.733,52 != sum(children) 74.519,72 (2 children); 81.02 est2026: parent 61.901,52 != sum(children) 25.000,00 (2 children); 81.02 trim1: parent 91.391,45 != sum(children) 10.025,79 (2 children); 81.02 total_2024: parent 318.456,97 != sum(children) 135.303,51 (2 children)</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="P582" s="5" t="inlineStr">
         <is>
-          <t>40 trim2: parent 23.500,00 != sum(children) 12.000,00 (2 children); 40 total_2024: parent 44.786,00 != sum(children) 12.000,00 (2 children)</t>
+          <t>40 total_2024: parent 44.786,00 != sum(children) 12.000,00 (2 children); 40 trim2: parent 23.500,00 != sum(children) 12.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="P604" s="5" t="inlineStr">
         <is>
-          <t>84.02 trim3: parent 63.461,00 != sum(children) 30.611,00 (3 children); 84.02 total_2024: parent 359.110,04 != sum(children) 179.947,24 (3 children); 84.02 trim1: parent 114.222,00 != sum(children) 39.047,42 (3 children); 84.02 est2024: parent 268.865,54 != sum(children) 138.229,96 (3 children); 84.02 est2027: parent 296.345,41 != sum(children) 163.798,71 (3 children); 84.02 est2026: parent 292.271,11 != sum(children) 159.279,92 (3 children); 84.02 trim2: parent 138.448,42 != sum(children) 90.807,00 (3 children); 84.02 trim4: parent 42.978,62 != sum(children) 19.481,82 (3 children)</t>
+          <t>84.02 trim3: parent 63.461,00 != sum(children) 30.611,00 (3 children); 84.02 est2027: parent 296.345,41 != sum(children) 163.798,71 (3 children); 84.02 est2024: parent 268.865,54 != sum(children) 138.229,96 (3 children); 84.02 trim4: parent 42.978,62 != sum(children) 19.481,82 (3 children); 84.02 trim2: parent 138.448,42 != sum(children) 90.807,00 (3 children); 84.02 est2026: parent 292.271,11 != sum(children) 159.279,92 (3 children); 84.02 trim1: parent 114.222,00 != sum(children) 39.047,42 (3 children); 84.02 total_2024: parent 359.110,04 != sum(children) 179.947,24 (3 children)</t>
         </is>
       </c>
     </row>
@@ -61607,12 +61607,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07.02 total_2024: parent 133.670,00 != sum(children) 242.770,00 (4 children)</t>
+          <t>07.02 est2027: parent 139.150,47 != sum(children) 252.723,57 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61637,12 +61637,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>07.02 trim1: parent 63.300,00 != sum(children) 112.900,00 (4 children)</t>
+          <t>07.02 est2024: parent 139.284,14 != sum(children) 252.966,34 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61667,12 +61667,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>07.02 est2024: parent 139.284,14 != sum(children) 252.966,34 (4 children)</t>
+          <t>07.02 trim4: parent 14.420,00 != sum(children) 25.770,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61697,12 +61697,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 139.150,47 != sum(children) 252.723,57 (4 children)</t>
+          <t>07.02 trim2: parent 15.950,00 != sum(children) 27.800,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61757,12 +61757,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07.02 trim2: parent 15.950,00 != sum(children) 27.800,00 (4 children)</t>
+          <t>07.02 trim1: parent 63.300,00 != sum(children) 112.900,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61787,12 +61787,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07.02 trim4: parent 14.420,00 != sum(children) 25.770,00 (4 children)</t>
+          <t>07.02 total_2024: parent 133.670,00 != sum(children) 242.770,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61872,12 +61872,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11.02 total_2024: parent 120.918,02 != sum(children) 106.507,02 (3 children)</t>
+          <t>11.02 est2027: parent 113.756,23 != sum(children) 112.122,23 (3 children)</t>
         </is>
       </c>
     </row>
@@ -61902,12 +61902,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11.02 trim1: parent 32.872,00 != sum(children) 27.491,00 (3 children)</t>
+          <t>11.02 est2024: parent 112.271,03 != sum(children) 110.637,03 (3 children)</t>
         </is>
       </c>
     </row>
@@ -61932,12 +61932,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11.02 est2024: parent 112.271,03 != sum(children) 110.637,03 (3 children)</t>
+          <t>11.02 trim4: parent 27.492,02 != sum(children) 25.762,02 (3 children)</t>
         </is>
       </c>
     </row>
@@ -61962,12 +61962,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11.02 est2027: parent 113.756,23 != sum(children) 112.122,23 (3 children)</t>
+          <t>11.02 trim2: parent 32.815,00 != sum(children) 27.491,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62022,12 +62022,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11.02 trim2: parent 32.815,00 != sum(children) 27.491,00 (3 children)</t>
+          <t>11.02 trim1: parent 32.872,00 != sum(children) 27.491,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62052,12 +62052,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11.02 trim4: parent 27.492,02 != sum(children) 25.762,02 (3 children)</t>
+          <t>11.02 total_2024: parent 120.918,02 != sum(children) 106.507,02 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62112,12 +62112,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.02 total_2024: parent 100.821,12 != sum(children) 15.000,00 (2 children)</t>
+          <t>36.02 est2027: parent 104.954,79 != sum(children) 15.615,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62142,12 +62142,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.02 trim1: parent 40.854,12 != sum(children) 5.400,00 (2 children)</t>
+          <t>36.02 est2024: parent 105.055,61 != sum(children) 15.630,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62172,12 +62172,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.02 est2024: parent 105.055,61 != sum(children) 15.630,00 (2 children)</t>
+          <t>36.02 trim4: parent 8.000,00 != sum(children) 3.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62202,12 +62202,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.02 est2027: parent 104.954,79 != sum(children) 15.615,00 (2 children)</t>
+          <t>36.02 trim2: parent 40.979,00 != sum(children) 3.400,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62262,12 +62262,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>36.02 trim2: parent 40.979,00 != sum(children) 3.400,00 (2 children)</t>
+          <t>36.02 trim1: parent 40.854,12 != sum(children) 5.400,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62292,12 +62292,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>36.02 trim4: parent 8.000,00 != sum(children) 3.000,00 (2 children)</t>
+          <t>36.02 total_2024: parent 100.821,12 != sum(children) 15.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62352,12 +62352,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>42.02 total_2024: parent 494.557,55 != sum(children) 306.943,20 (8 children)</t>
+          <t>42.02 est2027: parent 349.282,44 != sum(children) 153.975,90 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62382,12 +62382,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42.02 trim1: parent 97.369,51 != sum(children) 74.582,69 (8 children)</t>
+          <t>42.02 est2024: parent 349.617,95 != sum(children) 154.123,79 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62412,12 +62412,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42.02 est2024: parent 349.617,95 != sum(children) 154.123,79 (8 children)</t>
+          <t>42.02 trim4: parent 122.473,27 != sum(children) 65.473,27 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62442,12 +62442,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>42.02 est2027: parent 349.282,44 != sum(children) 153.975,90 (8 children)</t>
+          <t>42.02 trim2: parent 137.525,71 != sum(children) 98.198,18 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62502,12 +62502,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>42.02 trim2: parent 137.525,71 != sum(children) 98.198,18 (8 children)</t>
+          <t>42.02 trim1: parent 97.369,51 != sum(children) 74.582,69 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62532,12 +62532,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>42.02 trim4: parent 122.473,27 != sum(children) 65.473,27 (8 children)</t>
+          <t>42.02 total_2024: parent 494.557,55 != sum(children) 306.943,20 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62592,12 +62592,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>42.02.90 total_2024: parent 0,00 != sum(children) 187.614,35 (2 children)</t>
+          <t>42.02.90 est2027: parent 0,00 != sum(children) 195.306,54 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62622,12 +62622,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>42.02.90 trim1: parent 0,00 != sum(children) 22.786,82 (2 children)</t>
+          <t>42.02.90 est2024: parent 0,00 != sum(children) 195.494,16 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62652,12 +62652,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>42.02.90 est2024: parent 0,00 != sum(children) 195.494,16 (2 children)</t>
+          <t>42.02.90 trim4: parent 0,00 != sum(children) 57.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62682,12 +62682,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>42.02.90 est2027: parent 0,00 != sum(children) 195.306,54 (2 children)</t>
+          <t>42.02.90 trim2: parent 0,00 != sum(children) 39.327,53 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62742,12 +62742,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>42.02.90 trim2: parent 0,00 != sum(children) 39.327,53 (2 children)</t>
+          <t>42.02.90 trim1: parent 0,00 != sum(children) 22.786,82 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62772,12 +62772,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>42.02.90 trim4: parent 0,00 != sum(children) 57.000,00 (2 children)</t>
+          <t>42.02.90 total_2024: parent 0,00 != sum(children) 187.614,35 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62832,12 +62832,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>50.02 total_2024: parent 1.880.250,91 != sum(children) 602.137,95 (3 children)</t>
+          <t>50.02 est2027: parent 1.399.150,35 != sum(children) 463.986,64 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62862,12 +62862,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>50.02 trim1: parent 533.073,18 != sum(children) 136.972,96 (3 children)</t>
+          <t>50.02 est2024: parent 1.328.687,08 != sum(children) 406.235,28 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62892,12 +62892,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>50.02 est2024: parent 1.328.687,08 != sum(children) 406.235,28 (3 children)</t>
+          <t>50.02 trim4: parent 350.073,28 != sum(children) 106.300,38 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62922,12 +62922,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>50.02 est2027: parent 1.399.150,35 != sum(children) 463.986,64 (3 children)</t>
+          <t>50.02 trim2: parent 624.705,65 != sum(children) 253.340,97 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62982,12 +62982,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>50.02 trim2: parent 624.705,65 != sum(children) 253.340,97 (3 children)</t>
+          <t>50.02 trim1: parent 533.073,18 != sum(children) 136.972,96 (3 children)</t>
         </is>
       </c>
     </row>
@@ -63012,12 +63012,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>50.02 trim4: parent 350.073,28 != sum(children) 106.300,38 (3 children)</t>
+          <t>50.02 total_2024: parent 1.880.250,91 != sum(children) 602.137,95 (3 children)</t>
         </is>
       </c>
     </row>
@@ -63072,12 +63072,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>51.02 total_2024: parent 88.107,92 != sum(children) 4.013,62 (1 children)</t>
+          <t>51.02 est2027: parent 91.720,35 != sum(children) 4.178,18 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63102,12 +63102,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>51.02 trim1: parent 21.953,89 != sum(children) 724,69 (1 children)</t>
+          <t>51.02 est2024: parent 91.808,45 != sum(children) 4.182,19 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63132,12 +63132,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>51.02 est2024: parent 91.808,45 != sum(children) 4.182,19 (1 children)</t>
+          <t>51.02 trim4: parent 20.564,76 != sum(children) 1.430,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63162,12 +63162,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>51.02 est2027: parent 91.720,35 != sum(children) 4.178,18 (1 children)</t>
+          <t>51.02 trim2: parent 23.158,57 != sum(children) 1.541,73 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63222,12 +63222,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>51.02 trim2: parent 23.158,57 != sum(children) 1.541,73 (1 children)</t>
+          <t>51.02 trim1: parent 21.953,89 != sum(children) 724,69 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63252,12 +63252,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>51.02 trim4: parent 20.564,76 != sum(children) 1.430,00 (1 children)</t>
+          <t>51.02 total_2024: parent 88.107,92 != sum(children) 4.013,62 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63337,12 +63337,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 10.250,00 != sum(children) 4.575,00 (6 children)</t>
+          <t>20.01 trim4: parent 2.255,00 != sum(children) 1.055,00 (6 children)</t>
         </is>
       </c>
     </row>
@@ -63367,12 +63367,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 3.340,00 != sum(children) 1.465,00 (6 children)</t>
+          <t>20.01 trim2: parent 2.605,00 != sum(children) 1.305,00 (6 children)</t>
         </is>
       </c>
     </row>
@@ -63397,12 +63397,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20.01 trim2: parent 2.605,00 != sum(children) 1.305,00 (6 children)</t>
+          <t>20.01 trim1: parent 3.340,00 != sum(children) 1.465,00 (6 children)</t>
         </is>
       </c>
     </row>
@@ -63427,12 +63427,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 2.255,00 != sum(children) 1.055,00 (6 children)</t>
+          <t>20.01 total_2024: parent 10.250,00 != sum(children) 4.575,00 (6 children)</t>
         </is>
       </c>
     </row>
@@ -63487,12 +63487,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>54.02 total_2024: parent 19.336,99 != sum(children) 266,00 (1 children)</t>
+          <t>54.02 est2027: parent 4.431,53 != sum(children) 276,91 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63547,12 +63547,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>54.02 est2027: parent 4.431,53 != sum(children) 276,91 (1 children)</t>
+          <t>54.02 trim2: parent 1.277,80 != sum(children) 250,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63607,12 +63607,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>54.02 trim2: parent 1.277,80 != sum(children) 250,00 (1 children)</t>
+          <t>54.02 total_2024: parent 19.336,99 != sum(children) 266,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63687,12 +63687,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 9.836,90 != sum(children) 319,00 (1 children)</t>
+          <t>61.02 est2027: parent 10.240,22 != sum(children) 332,08 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63717,12 +63717,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.02 trim1: parent 2.869,50 != sum(children) 124,00 (1 children)</t>
+          <t>61.02 est2024: parent 10.250,05 != sum(children) 332,40 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63747,12 +63747,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.02 est2024: parent 10.250,05 != sum(children) 332,40 (1 children)</t>
+          <t>61.02 trim2: parent 2.807,60 != sum(children) 195,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63777,12 +63777,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.02 est2027: parent 10.240,22 != sum(children) 332,08 (1 children)</t>
+          <t>61.02 est2026: parent 10.289,40 != sum(children) 333,68 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63807,12 +63807,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.02 est2026: parent 10.289,40 != sum(children) 333,68 (1 children)</t>
+          <t>61.02 trim1: parent 2.869,50 != sum(children) 124,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63837,12 +63837,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.02 trim2: parent 2.807,60 != sum(children) 195,00 (1 children)</t>
+          <t>61.02 total_2024: parent 9.836,90 != sum(children) 319,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63892,12 +63892,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 792,90 != sum(children) 777,90 (7 children)</t>
+          <t>20 trim1: parent 324,00 != sum(children) 309,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63922,12 +63922,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20 trim1: parent 324,00 != sum(children) 309,00 (7 children)</t>
+          <t>20 total_2024: parent 792,90 != sum(children) 777,90 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63982,12 +63982,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>65.02 total_2024: parent 264.930,18 != sum(children) 25.276,37 (2 children)</t>
+          <t>65.02 est2027: parent 227.530,09 != sum(children) 24.826,74 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64012,12 +64012,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>65.02 trim1: parent 59.623,74 != sum(children) 11.333,34 (2 children)</t>
+          <t>65.02 est2024: parent 189.659,12 != sum(children) 24.834,73 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64042,12 +64042,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.02 est2024: parent 189.659,12 != sum(children) 24.834,73 (2 children)</t>
+          <t>65.02 trim4: parent 58.616,21 != sum(children) 903,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64072,12 +64072,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65.02 est2027: parent 227.530,09 != sum(children) 24.826,74 (2 children)</t>
+          <t>65.02 trim2: parent 73.807,61 != sum(children) 10.590,03 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64132,12 +64132,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>65.02 trim2: parent 73.807,61 != sum(children) 10.590,03 (2 children)</t>
+          <t>65.02 trim1: parent 59.623,74 != sum(children) 11.333,34 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64162,12 +64162,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>65.02 trim4: parent 58.616,21 != sum(children) 903,00 (2 children)</t>
+          <t>65.02 total_2024: parent 264.930,18 != sum(children) 25.276,37 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64247,12 +64247,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 24.546,80 != sum(children) 19.942,90 (7 children)</t>
+          <t>20.01 trim4: parent 5.383,92 != sum(children) 4.468,07 (7 children)</t>
         </is>
       </c>
     </row>
@@ -64277,12 +64277,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 8.129,03 != sum(children) 6.372,08 (7 children)</t>
+          <t>20.01 trim2: parent 6.022,48 != sum(children) 5.044,73 (7 children)</t>
         </is>
       </c>
     </row>
@@ -64307,12 +64307,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>20.01 trim2: parent 6.022,48 != sum(children) 5.044,73 (7 children)</t>
+          <t>20.01 trim1: parent 8.129,03 != sum(children) 6.372,08 (7 children)</t>
         </is>
       </c>
     </row>
@@ -64337,12 +64337,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 5.383,92 != sum(children) 4.468,07 (7 children)</t>
+          <t>20.01 total_2024: parent 24.546,80 != sum(children) 19.942,90 (7 children)</t>
         </is>
       </c>
     </row>
@@ -64367,12 +64367,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>59 total_2024: parent 319,90 != sum(children) 309,90 (3 children)</t>
+          <t>59 trim2: parent 78,80 != sum(children) 68,80 (3 children)</t>
         </is>
       </c>
     </row>
@@ -64397,12 +64397,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>59 trim2: parent 78,80 != sum(children) 68,80 (3 children)</t>
+          <t>59 total_2024: parent 319,90 != sum(children) 309,90 (3 children)</t>
         </is>
       </c>
     </row>
@@ -64457,12 +64457,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>66.02 total_2024: parent 171.081,32 != sum(children) 26.902,17 (2 children)</t>
+          <t>66.02 est2027: parent 128.221,96 != sum(children) 10.503,46 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64487,12 +64487,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>66.02 trim1: parent 26.927,54 != sum(children) 2.839,92 (2 children)</t>
+          <t>66.02 est2024: parent 128.336,50 != sum(children) 10.504,91 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64517,12 +64517,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>66.02 est2024: parent 128.336,50 != sum(children) 10.504,91 (2 children)</t>
+          <t>66.02 trim4: parent 63.590,29 != sum(children) 17.614,44 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64547,12 +64547,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>66.02 est2027: parent 128.221,96 != sum(children) 10.503,46 (2 children)</t>
+          <t>66.02 trim2: parent 27.913,49 != sum(children) 5.647,81 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64607,12 +64607,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>66.02 trim2: parent 27.913,49 != sum(children) 5.647,81 (2 children)</t>
+          <t>66.02 trim1: parent 26.927,54 != sum(children) 2.839,92 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64637,12 +64637,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>66.02 trim4: parent 63.590,29 != sum(children) 17.614,44 (2 children)</t>
+          <t>66.02 total_2024: parent 171.081,32 != sum(children) 26.902,17 (2 children)</t>
         </is>
       </c>
     </row>
@@ -64722,12 +64722,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>10.01 total_2024: parent 8.726,85 != sum(children) 8.390,85 (4 children)</t>
+          <t>10.01 trim4: parent 1.890,85 != sum(children) 1.807,85 (4 children)</t>
         </is>
       </c>
     </row>
@@ -64752,12 +64752,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>10.01 trim1: parent 2.215,00 != sum(children) 2.130,00 (4 children)</t>
+          <t>10.01 trim2: parent 2.362,00 != sum(children) 2.278,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -64782,12 +64782,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10.01 trim2: parent 2.362,00 != sum(children) 2.278,00 (4 children)</t>
+          <t>10.01 trim1: parent 2.215,00 != sum(children) 2.130,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -64812,12 +64812,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>10.01 trim4: parent 1.890,85 != sum(children) 1.807,85 (4 children)</t>
+          <t>10.01 total_2024: parent 8.726,85 != sum(children) 8.390,85 (4 children)</t>
         </is>
       </c>
     </row>
@@ -64842,12 +64842,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60 trim2: parent 12.827,53 != sum(children) 2.212,70 (1 children)</t>
+          <t>60 trim3: parent 41.000,00 != sum(children) 6.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -64872,12 +64872,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60 trim3: parent 41.000,00 != sum(children) 6.000,00 (1 children)</t>
+          <t>60 total_2024: parent 95.827,53 != sum(children) 15.212,70 (1 children)</t>
         </is>
       </c>
     </row>
@@ -64902,12 +64902,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60 trim4: parent 42.000,00 != sum(children) 7.000,00 (1 children)</t>
+          <t>60 trim2: parent 12.827,53 != sum(children) 2.212,70 (1 children)</t>
         </is>
       </c>
     </row>
@@ -64932,12 +64932,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60 total_2024: parent 95.827,53 != sum(children) 15.212,70 (1 children)</t>
+          <t>60 trim4: parent 42.000,00 != sum(children) 7.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -64992,12 +64992,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>67.02 total_2024: parent 98.281,69 != sum(children) 27.660,18 (1 children)</t>
+          <t>67.02 est2027: parent 101.417,63 != sum(children) 28.794,26 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65022,12 +65022,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>67.02 trim1: parent 23.973,71 != sum(children) 6.772,48 (1 children)</t>
+          <t>67.02 est2024: parent 101.498,43 != sum(children) 28.821,91 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65052,12 +65052,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>67.02 est2024: parent 101.498,43 != sum(children) 28.821,91 (1 children)</t>
+          <t>67.02 trim4: parent 20.947,00 != sum(children) 4.626,20 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65082,12 +65082,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>67.02 est2027: parent 101.417,63 != sum(children) 28.794,26 (1 children)</t>
+          <t>67.02 trim2: parent 29.149,86 != sum(children) 8.654,92 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65142,12 +65142,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 29.149,86 != sum(children) 8.654,92 (1 children)</t>
+          <t>67.02 trim1: parent 23.973,71 != sum(children) 6.772,48 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65172,12 +65172,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>67.02 trim4: parent 20.947,00 != sum(children) 4.626,20 (1 children)</t>
+          <t>67.02 total_2024: parent 98.281,69 != sum(children) 27.660,18 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65227,12 +65227,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>71 total_2024: parent 27.660,18 != sum(children) 27.110,18 (2 children)</t>
+          <t>71 trim4: parent 4.626,20 != sum(children) 4.376,20 (2 children)</t>
         </is>
       </c>
     </row>
@@ -65257,12 +65257,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>71 trim1: parent 6.772,48 != sum(children) 6.622,48 (2 children)</t>
+          <t>71 trim2: parent 8.654,92 != sum(children) 8.504,92 (2 children)</t>
         </is>
       </c>
     </row>
@@ -65287,12 +65287,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>71 trim2: parent 8.654,92 != sum(children) 8.504,92 (2 children)</t>
+          <t>71 trim1: parent 6.772,48 != sum(children) 6.622,48 (2 children)</t>
         </is>
       </c>
     </row>
@@ -65317,12 +65317,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>71 trim4: parent 4.626,20 != sum(children) 4.376,20 (2 children)</t>
+          <t>71 total_2024: parent 27.660,18 != sum(children) 27.110,18 (2 children)</t>
         </is>
       </c>
     </row>
@@ -65377,12 +65377,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>68.02 total_2024: parent 70.976,99 != sum(children) 57.319,51 (3 children)</t>
+          <t>68.02 est2027: parent 71.612,72 != sum(children) 57.395,26 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65407,12 +65407,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>68.02 trim1: parent 21.857,30 != sum(children) 17.182,00 (3 children)</t>
+          <t>68.02 est2024: parent 71.628,73 != sum(children) 57.397,64 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65437,12 +65437,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>68.02 est2024: parent 71.628,73 != sum(children) 57.397,64 (3 children)</t>
+          <t>68.02 trim4: parent 14.328,79 != sum(children) 12.098,51 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65467,12 +65467,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>68.02 est2027: parent 71.612,72 != sum(children) 57.395,26 (3 children)</t>
+          <t>68.02 trim2: parent 18.660,00 != sum(children) 15.150,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65527,12 +65527,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>68.02 trim2: parent 18.660,00 != sum(children) 15.150,00 (3 children)</t>
+          <t>68.02 trim1: parent 21.857,30 != sum(children) 17.182,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65557,12 +65557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>68.02 trim4: parent 14.328,79 != sum(children) 12.098,51 (3 children)</t>
+          <t>68.02 total_2024: parent 70.976,99 != sum(children) 57.319,51 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65587,12 +65587,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>68.02 total_2024: parent 70.976,99 != sum(children) 835,00 (1 children)</t>
+          <t>68.02 est2027: parent 71.612,72 != sum(children) 869,24 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65617,12 +65617,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>68.02 trim1: parent 21.857,30 != sum(children) 775,00 (1 children)</t>
+          <t>68.02 est2024: parent 71.628,73 != sum(children) 870,07 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65647,12 +65647,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>68.02 est2024: parent 71.628,73 != sum(children) 870,07 (1 children)</t>
+          <t>68.02 trim2: parent 18.660,00 != sum(children) 60,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65677,12 +65677,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>68.02 est2027: parent 71.612,72 != sum(children) 869,24 (1 children)</t>
+          <t>68.02 est2026: parent 71.692,91 != sum(children) 873,41 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65707,12 +65707,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>68.02 est2026: parent 71.692,91 != sum(children) 873,41 (1 children)</t>
+          <t>68.02 trim1: parent 21.857,30 != sum(children) 775,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65737,12 +65737,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>68.02 trim2: parent 18.660,00 != sum(children) 60,00 (1 children)</t>
+          <t>68.02 total_2024: parent 70.976,99 != sum(children) 835,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65792,12 +65792,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 3.540,18 != sum(children) 3.532,18 (9 children)</t>
+          <t>20 trim1: parent 1.401,00 != sum(children) 1.393,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -65822,12 +65822,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>20 trim1: parent 1.401,00 != sum(children) 1.393,00 (9 children)</t>
+          <t>20 total_2024: parent 3.540,18 != sum(children) 3.532,18 (9 children)</t>
         </is>
       </c>
     </row>
@@ -65882,12 +65882,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 343.391,66 != sum(children) 193.691,53 (3 children)</t>
+          <t>70.02 est2027: parent 296.502,92 != sum(children) 202.186,67 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65912,12 +65912,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>70.02 trim1: parent 127.976,36 != sum(children) 64.193,65 (3 children)</t>
+          <t>70.02 est2024: parent 264.090,49 != sum(children) 169.702,84 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65942,12 +65942,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>70.02 est2024: parent 264.090,49 != sum(children) 169.702,84 (3 children)</t>
+          <t>70.02 trim4: parent 52.048,89 != sum(children) 30.828,69 (3 children)</t>
         </is>
       </c>
     </row>
@@ -65972,12 +65972,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>70.02 est2027: parent 296.502,92 != sum(children) 202.186,67 (3 children)</t>
+          <t>70.02 trim2: parent 101.467,10 != sum(children) 60.632,08 (3 children)</t>
         </is>
       </c>
     </row>
@@ -66032,12 +66032,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>70.02 trim2: parent 101.467,10 != sum(children) 60.632,08 (3 children)</t>
+          <t>70.02 trim1: parent 127.976,36 != sum(children) 64.193,65 (3 children)</t>
         </is>
       </c>
     </row>
@@ -66062,12 +66062,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>70.02 trim4: parent 52.048,89 != sum(children) 30.828,69 (3 children)</t>
+          <t>70.02 total_2024: parent 343.391,66 != sum(children) 193.691,53 (3 children)</t>
         </is>
       </c>
     </row>
@@ -66142,12 +66142,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 74.355,79 != sum(children) 73.085,79 (2 children)</t>
+          <t>74.02 est2027: parent 64.283,43 != sum(children) 62.961,35 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66172,12 +66172,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>74.02 trim1: parent 20.429,79 != sum(children) 19.184,79 (2 children)</t>
+          <t>74.02 est2024: parent 59.292,34 != sum(children) 57.969,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66202,12 +66202,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>74.02 est2024: parent 59.292,34 != sum(children) 57.969,00 (2 children)</t>
+          <t>74.02 trim2: parent 20.542,25 != sum(children) 20.517,25 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66232,12 +66232,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>74.02 est2027: parent 64.283,43 != sum(children) 62.961,35 (2 children)</t>
+          <t>74.02 est2026: parent 64.328,00 != sum(children) 62.999,58 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66262,12 +66262,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>74.02 est2026: parent 64.328,00 != sum(children) 62.999,58 (2 children)</t>
+          <t>74.02 trim1: parent 20.429,79 != sum(children) 19.184,79 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66292,12 +66292,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>74.02 trim2: parent 20.542,25 != sum(children) 20.517,25 (2 children)</t>
+          <t>74.02 total_2024: parent 74.355,79 != sum(children) 73.085,79 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66352,12 +66352,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 74.355,79 != sum(children) 866,20 (1 children)</t>
+          <t>74.02 est2027: parent 64.283,43 != sum(children) 901,71 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66382,12 +66382,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>74.02 trim1: parent 20.429,79 != sum(children) 302,20 (1 children)</t>
+          <t>74.02 est2024: parent 59.292,34 != sum(children) 902,58 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66412,12 +66412,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>74.02 est2024: parent 59.292,34 != sum(children) 902,58 (1 children)</t>
+          <t>74.02 trim4: parent 12.427,50 != sum(children) 31,50 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66442,12 +66442,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>74.02 est2027: parent 64.283,43 != sum(children) 901,71 (1 children)</t>
+          <t>74.02 trim2: parent 20.542,25 != sum(children) 334,25 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66502,12 +66502,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>74.02 trim2: parent 20.542,25 != sum(children) 334,25 (1 children)</t>
+          <t>74.02 trim1: parent 20.429,79 != sum(children) 302,20 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66532,12 +66532,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>74.02 trim4: parent 12.427,50 != sum(children) 31,50 (1 children)</t>
+          <t>74.02 total_2024: parent 74.355,79 != sum(children) 866,20 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66617,12 +66617,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>80.02 total_2024: parent 13.374,46 != sum(children) 704.315,93 (2 children)</t>
+          <t>80.02 est2027: parent 9.351,30 != sum(children) 375.655,80 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66647,12 +66647,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>80.02 trim1: parent 3.751,80 != sum(children) 213.117,05 (2 children)</t>
+          <t>80.02 est2024: parent 9.358,41 != sum(children) 367.850,09 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66677,12 +66677,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>80.02 est2024: parent 9.358,41 != sum(children) 367.850,09 (2 children)</t>
+          <t>80.02 trim4: parent 6.626,73 != sum(children) 87.776,08 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66707,12 +66707,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>80.02 est2027: parent 9.351,30 != sum(children) 375.655,80 (2 children)</t>
+          <t>80.02 trim2: parent 1.508,43 != sum(children) 306.198,80 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66767,12 +66767,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>80.02 trim2: parent 1.508,43 != sum(children) 306.198,80 (2 children)</t>
+          <t>80.02 trim1: parent 3.751,80 != sum(children) 213.117,05 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66797,12 +66797,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>80.02 trim4: parent 6.626,73 != sum(children) 87.776,08 (2 children)</t>
+          <t>80.02 total_2024: parent 13.374,46 != sum(children) 704.315,93 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66857,12 +66857,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>80.02 total_2024: parent 13.374,46 != sum(children) 7.057,13 (2 children)</t>
+          <t>80.02 est2027: parent 9.351,30 != sum(children) 2.818,68 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66887,12 +66887,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>80.02 trim1: parent 3.751,80 != sum(children) 834,47 (2 children)</t>
+          <t>80.02 est2024: parent 9.358,41 != sum(children) 2.819,52 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66917,12 +66917,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>80.02 est2024: parent 9.358,41 != sum(children) 2.819,52 (2 children)</t>
+          <t>80.02 trim4: parent 6.626,73 != sum(children) 5.626,73 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66947,12 +66947,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>80.02 est2027: parent 9.351,30 != sum(children) 2.818,68 (2 children)</t>
+          <t>80.02 trim2: parent 1.508,43 != sum(children) 108,43 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67007,12 +67007,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>80.02 trim2: parent 1.508,43 != sum(children) 108,43 (2 children)</t>
+          <t>80.02 trim1: parent 3.751,80 != sum(children) 834,47 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67037,12 +67037,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>80.02 trim4: parent 6.626,73 != sum(children) 5.626,73 (2 children)</t>
+          <t>80.02 total_2024: parent 13.374,46 != sum(children) 7.057,13 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67122,12 +67122,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>81.02 total_2024: parent 318.456,97 != sum(children) 135.303,51 (2 children)</t>
+          <t>81.02 est2027: parent 60.607,79 != sum(children) 24.500,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67152,12 +67152,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>81.02 trim1: parent 91.391,45 != sum(children) 10.025,79 (2 children)</t>
+          <t>81.02 est2024: parent 80.267,73 != sum(children) 24.757,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67182,12 +67182,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>81.02 est2024: parent 80.267,73 != sum(children) 24.757,00 (2 children)</t>
+          <t>81.02 trim4: parent 31.544,00 != sum(children) 25.758,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67212,12 +67212,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>81.02 est2027: parent 60.607,79 != sum(children) 24.500,00 (2 children)</t>
+          <t>81.02 trim2: parent 164.733,52 != sum(children) 74.519,72 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67272,12 +67272,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>81.02 trim2: parent 164.733,52 != sum(children) 74.519,72 (2 children)</t>
+          <t>81.02 trim1: parent 91.391,45 != sum(children) 10.025,79 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67302,12 +67302,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>81.02 trim4: parent 31.544,00 != sum(children) 25.758,00 (2 children)</t>
+          <t>81.02 total_2024: parent 318.456,97 != sum(children) 135.303,51 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67357,12 +67357,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>40 trim2: parent 23.500,00 != sum(children) 12.000,00 (2 children)</t>
+          <t>40 total_2024: parent 44.786,00 != sum(children) 12.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67387,12 +67387,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>40 total_2024: parent 44.786,00 != sum(children) 12.000,00 (2 children)</t>
+          <t>40 trim2: parent 23.500,00 != sum(children) 12.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67447,12 +67447,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 359.110,04 != sum(children) 179.947,24 (3 children)</t>
+          <t>84.02 est2027: parent 296.345,41 != sum(children) 163.798,71 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67477,12 +67477,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>84.02 trim1: parent 114.222,00 != sum(children) 39.047,42 (3 children)</t>
+          <t>84.02 est2024: parent 268.865,54 != sum(children) 138.229,96 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67507,12 +67507,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>84.02 est2024: parent 268.865,54 != sum(children) 138.229,96 (3 children)</t>
+          <t>84.02 trim4: parent 42.978,62 != sum(children) 19.481,82 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67537,12 +67537,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>84.02 est2027: parent 296.345,41 != sum(children) 163.798,71 (3 children)</t>
+          <t>84.02 trim2: parent 138.448,42 != sum(children) 90.807,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67597,12 +67597,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>84.02 trim2: parent 138.448,42 != sum(children) 90.807,00 (3 children)</t>
+          <t>84.02 trim1: parent 114.222,00 != sum(children) 39.047,42 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67627,12 +67627,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>84.02 trim4: parent 42.978,62 != sum(children) 19.481,82 (3 children)</t>
+          <t>84.02 total_2024: parent 359.110,04 != sum(children) 179.947,24 (3 children)</t>
         </is>
       </c>
     </row>
@@ -68272,7 +68272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -68298,7 +68298,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -68398,27 +68398,27 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Pagini asteptate</t>
+          <t>Linii anexe separate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Pagini selectate</t>
+          <t>Celule numerice anexe separate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Pagini procesate</t>
+          <t>Pagini asteptate</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -68428,115 +68428,111 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDF complet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
+          <t>Pagini procesate</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1192</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>% curat</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>94.8</v>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>198</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>% curat</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Informatii</t>
+          <t>Erori</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Schema publicare</t>
+          <t>Avertismente</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Bundle conversie</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>82909268ff64a071df233eac</t>
-        </is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 sursa</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5a0911c5dd8933d54644d08d2ba10f4f25cf9f34b382d8d294fc2cf3291b8754</t>
-        </is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Format sursa</t>
+          <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>25a5503b552cc1c3ac7a7b89</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 PDF sursa</t>
+          <t>SHA-256 sursa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -68548,10 +68544,34 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Format sursa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5a0911c5dd8933d54644d08d2ba10f4f25cf9f34b382d8d294fc2cf3291b8754</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>local, pag. 1-46, 1286 linii</t>
         </is>
